--- a/data/processed/positivacao/2025-10_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-10_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -27207,7 +27207,7 @@
     <row r="1034">
       <c r="A1034" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1034" t="inlineStr"/>
@@ -38325,7 +38325,7 @@
     <row r="1462">
       <c r="A1462" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1462" t="inlineStr"/>
@@ -66619,7 +66619,7 @@
     <row r="2551">
       <c r="A2551" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2551" t="inlineStr"/>
@@ -68186,12 +68186,12 @@
       <c r="A2612" t="inlineStr"/>
       <c r="B2612" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 4 cliente(s), não positivou 84 cliente(s) - Total vendido: R$ 3.720,45
+          <t>Vendedor 1 - VENDEDOR 01: positivou 4 cliente(s), não positivou 84 cliente(s) - Total vendido: R$ 3.720,45
 Vendedor 18 - LOJA: positivou 299 cliente(s), não positivou 637 cliente(s) - Total vendido: R$ 98.368,75
-Vendedor 3 - FERNANDA: positivou 132 cliente(s), não positivou 295 cliente(s) - Total vendido: R$ 155.753,10
-Vendedor 4 - DANIELA: positivou 128 cliente(s), não positivou 516 cliente(s) - Total vendido: R$ 76.563,13
+Vendedor 3 - VENDEDOR 03: positivou 132 cliente(s), não positivou 295 cliente(s) - Total vendido: R$ 155.753,10
+Vendedor 4 - VENDEDOR 04: positivou 128 cliente(s), não positivou 516 cliente(s) - Total vendido: R$ 76.563,13
 Vendedor 5 - SITE: positivou 2 cliente(s), não positivou 441 cliente(s) - Total vendido: R$ 46,92
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 59 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 59 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2612" t="inlineStr"/>
